--- a/public/test-data/CLAIM - Fastenal (real format) Mar2026.xlsx
+++ b/public/test-data/CLAIM - Fastenal (real format) Mar2026.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,28 +448,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B2" t="str">
-        <v>MN008200001</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46086</v>
+        <v>MN008200101</v>
+      </c>
+      <c r="C2">
+        <v>46084</v>
       </c>
       <c r="D2" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E2" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F2" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F2">
         <v>100003</v>
       </c>
       <c r="G2" t="str">
-        <v>04017001</v>
+        <v>04017578</v>
       </c>
       <c r="H2" t="str">
         <v>0304-C-04</v>
       </c>
       <c r="I2" t="str">
-        <v>1/4 Comp Union</v>
+        <v>1/4 COMP UNION BRASS</v>
       </c>
       <c r="J2" t="str">
         <v>0000131563</v>
@@ -493,28 +492,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B3" t="str">
-        <v>MN008200001</v>
-      </c>
-      <c r="C3" s="1">
-        <v>46086</v>
+        <v>MN008200101</v>
+      </c>
+      <c r="C3">
+        <v>46084</v>
       </c>
       <c r="D3" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E3" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F3" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F3">
         <v>100003</v>
       </c>
       <c r="G3" t="str">
-        <v>04017002</v>
+        <v>04017579</v>
       </c>
       <c r="H3" t="str">
         <v>0304-C-06</v>
       </c>
       <c r="I3" t="str">
-        <v>3/8 Comp Union</v>
+        <v>3/8 COMP UNION BRASS</v>
       </c>
       <c r="J3" t="str">
         <v>0000131563</v>
@@ -529,7 +528,7 @@
         <v>75</v>
       </c>
       <c r="N3">
-        <v>8.25</v>
+        <v>8.250000000000004</v>
       </c>
     </row>
     <row r="4">
@@ -537,28 +536,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B4" t="str">
-        <v>MN008200002</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46091</v>
+        <v>MN008200203</v>
+      </c>
+      <c r="C4">
+        <v>46088</v>
       </c>
       <c r="D4" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E4" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F4" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F4">
         <v>100003</v>
       </c>
       <c r="G4" t="str">
-        <v>04017003</v>
+        <v>04017580</v>
       </c>
       <c r="H4" t="str">
         <v>0304-C-08</v>
       </c>
       <c r="I4" t="str">
-        <v>1/2 Comp Union</v>
+        <v>1/2 COMP UNION BRASS</v>
       </c>
       <c r="J4" t="str">
         <v>0000131563</v>
@@ -573,7 +572,7 @@
         <v>200</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>34.00000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -581,28 +580,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B5" t="str">
-        <v>MN008200003</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46093</v>
+        <v>MN008200203</v>
+      </c>
+      <c r="C5">
+        <v>46088</v>
       </c>
       <c r="D5" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E5" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F5" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F5">
         <v>100003</v>
       </c>
       <c r="G5" t="str">
-        <v>04017004</v>
+        <v>04017581</v>
       </c>
       <c r="H5" t="str">
         <v>0305-B-08</v>
       </c>
       <c r="I5" t="str">
-        <v>1/2 Brass Comp Union</v>
+        <v>1/2 BRASS COMP UNION</v>
       </c>
       <c r="J5" t="str">
         <v>0000131563</v>
@@ -617,7 +616,7 @@
         <v>50</v>
       </c>
       <c r="N5">
-        <v>15</v>
+        <v>14.999999999999996</v>
       </c>
     </row>
     <row r="6">
@@ -625,28 +624,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B6" t="str">
-        <v>MN008200004</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46096</v>
+        <v>MN008200305</v>
+      </c>
+      <c r="C6">
+        <v>46093</v>
       </c>
       <c r="D6" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E6" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F6" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F6">
         <v>100003</v>
       </c>
       <c r="G6" t="str">
-        <v>04017005</v>
+        <v>04017582</v>
       </c>
       <c r="H6" t="str">
         <v>1100-C-12</v>
       </c>
       <c r="I6" t="str">
-        <v>3/4 Male Connector</v>
+        <v>3/4 MALE CONNECTOR SS</v>
       </c>
       <c r="J6" t="str">
         <v>0000131563</v>
@@ -669,28 +668,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B7" t="str">
-        <v>MN008200005</v>
-      </c>
-      <c r="C7" s="1">
-        <v>46099</v>
+        <v>MN008200410</v>
+      </c>
+      <c r="C7">
+        <v>46095</v>
       </c>
       <c r="D7" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E7" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F7" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F7">
         <v>100003</v>
       </c>
       <c r="G7" t="str">
-        <v>04017006</v>
+        <v>04017583</v>
       </c>
       <c r="H7" t="str">
         <v>1100-D-16</v>
       </c>
       <c r="I7" t="str">
-        <v>1in Male Connector</v>
+        <v>1IN MALE CONNECTOR SS</v>
       </c>
       <c r="J7" t="str">
         <v>0000131563</v>
@@ -705,7 +704,7 @@
         <v>20</v>
       </c>
       <c r="N7">
-        <v>32</v>
+        <v>31.999999999999993</v>
       </c>
     </row>
     <row r="8">
@@ -713,28 +712,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B8" t="str">
-        <v>MN008200006</v>
-      </c>
-      <c r="C8" s="1">
-        <v>46101</v>
+        <v>MN008200512</v>
+      </c>
+      <c r="C8">
+        <v>46099</v>
       </c>
       <c r="D8" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E8" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F8" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F8">
         <v>100003</v>
       </c>
       <c r="G8" t="str">
-        <v>04017007</v>
+        <v>04017584</v>
       </c>
       <c r="H8" t="str">
         <v>2403-12-12</v>
       </c>
       <c r="I8" t="str">
-        <v>3/4x3/4 Male Elbow</v>
+        <v>3/4X3/4 MALE ELBOW</v>
       </c>
       <c r="J8" t="str">
         <v>0000131563</v>
@@ -749,7 +748,7 @@
         <v>15</v>
       </c>
       <c r="N8">
-        <v>27</v>
+        <v>26.999999999999996</v>
       </c>
     </row>
     <row r="9">
@@ -757,28 +756,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B9" t="str">
-        <v>MN008200007</v>
-      </c>
-      <c r="C9" s="1">
-        <v>46103</v>
+        <v>MN008200615</v>
+      </c>
+      <c r="C9">
+        <v>46102</v>
       </c>
       <c r="D9" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E9" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F9" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F9">
         <v>100003</v>
       </c>
       <c r="G9" t="str">
-        <v>04017008</v>
+        <v>04017585</v>
       </c>
       <c r="H9" t="str">
         <v>2403-16-16</v>
       </c>
       <c r="I9" t="str">
-        <v>1x1 Male Elbow</v>
+        <v>1X1 MALE ELBOW</v>
       </c>
       <c r="J9" t="str">
         <v>0000131563</v>
@@ -801,28 +800,28 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B10" t="str">
-        <v>MN008200008</v>
-      </c>
-      <c r="C10" s="1">
-        <v>46106</v>
+        <v>MN008200720</v>
+      </c>
+      <c r="C10">
+        <v>46105</v>
       </c>
       <c r="D10" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E10" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F10" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F10">
         <v>100003</v>
       </c>
       <c r="G10" t="str">
-        <v>04017001</v>
+        <v>04017578</v>
       </c>
       <c r="H10" t="str">
         <v>0304-C-04</v>
       </c>
       <c r="I10" t="str">
-        <v>1/4 Comp Union</v>
+        <v>1/4 COMP UNION BRASS</v>
       </c>
       <c r="J10" t="str">
         <v>0000131563</v>
@@ -845,43 +844,37 @@
         <v>BRENNAN INDUSTRIES, INC</v>
       </c>
       <c r="B11" t="str">
-        <v>MN008200009</v>
-      </c>
-      <c r="C11" s="1">
-        <v>46107</v>
+        <v>MN008200825</v>
+      </c>
+      <c r="C11">
+        <v>46106</v>
       </c>
       <c r="D11" t="str">
-        <v>BAY-001</v>
+        <v>BAY0010097</v>
       </c>
       <c r="E11" t="str">
-        <v>Bayshore</v>
-      </c>
-      <c r="F11" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F11">
         <v>100003</v>
       </c>
-      <c r="G11" t="str">
-        <v>04099999</v>
+      <c r="G11">
+        <v>4017580</v>
       </c>
       <c r="H11" t="str">
-        <v>FAKE-PART-999</v>
+        <v>0304-C-08</v>
       </c>
       <c r="I11" t="str">
-        <v>Unknown Widget</v>
+        <v>1/2 COMP UNION BRASS</v>
       </c>
       <c r="J11" t="str">
         <v>0000131563</v>
       </c>
-      <c r="K11">
-        <v>10</v>
-      </c>
       <c r="L11">
-        <v>7.5</v>
+        <v>0.63</v>
       </c>
       <c r="M11">
-        <v>25</v>
-      </c>
-      <c r="N11">
-        <v>62.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -891,7 +884,7 @@
       <c r="B12" t="str">
         <v>PA0530001</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>46096</v>
       </c>
       <c r="D12" t="str">
@@ -901,7 +894,7 @@
         <v>DEEP WELL SERVICES</v>
       </c>
       <c r="F12" t="str">
-        <v>999999</v>
+        <v>104676</v>
       </c>
       <c r="G12" t="str">
         <v>421328</v>
@@ -910,7 +903,7 @@
         <v>6400-08-12-O</v>
       </c>
       <c r="I12" t="str">
-        <v>STRT THD OCON 1/2X3/4</v>
+        <v>STRT THD OCON1/2X3/4</v>
       </c>
       <c r="J12" t="str">
         <v>0000131563</v>
@@ -919,18 +912,150 @@
         <v>3.24</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.3833</v>
       </c>
       <c r="M12">
         <v>20</v>
       </c>
       <c r="N12">
-        <v>37.2</v>
+        <v>37.134</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BRENNAN INDUSTRIES, INC</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PA0530002</v>
+      </c>
+      <c r="C13">
+        <v>46098</v>
+      </c>
+      <c r="D13" t="str">
+        <v>PA0520050</v>
+      </c>
+      <c r="E13" t="str">
+        <v>DEEP WELL SERVICES</v>
+      </c>
+      <c r="F13" t="str">
+        <v>999999</v>
+      </c>
+      <c r="G13" t="str">
+        <v>420957</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2501-04-04-FG</v>
+      </c>
+      <c r="I13" t="str">
+        <v>90M ELBOW 1/4T 1/4M</v>
+      </c>
+      <c r="J13" t="str">
+        <v>0000131563</v>
+      </c>
+      <c r="K13">
+        <v>1.78</v>
+      </c>
+      <c r="L13">
+        <v>0.8667</v>
+      </c>
+      <c r="M13">
+        <v>50</v>
+      </c>
+      <c r="N13">
+        <v>45.665</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BRENNAN INDUSTRIES, INC</v>
+      </c>
+      <c r="B14" t="str">
+        <v>WIANT208999</v>
+      </c>
+      <c r="C14">
+        <v>46091</v>
+      </c>
+      <c r="D14" t="str">
+        <v>WIANT0138</v>
+      </c>
+      <c r="E14" t="str">
+        <v>CLEEREMAN INDUSTRIES INC.</v>
+      </c>
+      <c r="F14" t="str">
+        <v>104438</v>
+      </c>
+      <c r="G14" t="str">
+        <v>421062</v>
+      </c>
+      <c r="H14" t="str">
+        <v>6801-08-12-NWO-FG</v>
+      </c>
+      <c r="I14" t="str">
+        <v>ST OR90 1/2T 3/4P</v>
+      </c>
+      <c r="J14" t="str">
+        <v>0000131563</v>
+      </c>
+      <c r="K14">
+        <v>5.78</v>
+      </c>
+      <c r="L14">
+        <v>3.69</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BRENNAN INDUSTRIES, INC</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MN008200101</v>
+      </c>
+      <c r="C15">
+        <v>46084</v>
+      </c>
+      <c r="D15" t="str">
+        <v>BAY0010097</v>
+      </c>
+      <c r="E15" t="str">
+        <v>BAYSHORE - DIRECTED BUY</v>
+      </c>
+      <c r="F15">
+        <v>100003</v>
+      </c>
+      <c r="G15" t="str">
+        <v>04017578</v>
+      </c>
+      <c r="H15" t="str">
+        <v>0304-C-04</v>
+      </c>
+      <c r="I15" t="str">
+        <v>1/4 COMP UNION BRASS</v>
+      </c>
+      <c r="J15" t="str">
+        <v>0000131563</v>
+      </c>
+      <c r="K15">
+        <v>0.46</v>
+      </c>
+      <c r="L15">
+        <v>0.33</v>
+      </c>
+      <c r="M15">
+        <v>50</v>
+      </c>
+      <c r="N15">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N15"/>
   </ignoredErrors>
 </worksheet>
 </file>